--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\27,07,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37162B5B-2782-480B-AA86-F3A7C4DE1303}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B801F01-9AA7-4DC4-96B7-99DFA53CE13A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="176">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -660,7 +660,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,6 +701,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -737,7 +743,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -763,6 +769,10 @@
     <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -5927,7 +5937,7 @@
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>14670</v>
+        <v>14584</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
@@ -5974,7 +5984,7 @@
       <c r="AF5" s="7"/>
       <c r="AG5" s="3">
         <f>SUM(AG6:AG485)</f>
-        <v>5963.6900000000014</v>
+        <v>5939.6100000000015</v>
       </c>
       <c r="AH5" s="7"/>
       <c r="AI5" s="7"/>
@@ -15255,99 +15265,100 @@
       <c r="AY88" s="7"/>
     </row>
     <row r="89" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="25">
         <v>86</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="25">
         <v>15</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="25">
         <v>92</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="25">
         <v>3</v>
       </c>
-      <c r="G89" s="8">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H89" s="7">
+      <c r="G89" s="26">
+        <v>0</v>
+      </c>
+      <c r="H89" s="25">
         <v>45</v>
       </c>
-      <c r="I89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7">
+      <c r="I89" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25">
         <v>162</v>
       </c>
-      <c r="L89" s="7">
+      <c r="L89" s="25">
         <f t="shared" si="11"/>
         <v>-70</v>
       </c>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7">
+      <c r="M89" s="25"/>
+      <c r="N89" s="25"/>
+      <c r="O89" s="25">
         <v>187</v>
       </c>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7">
+      <c r="P89" s="25"/>
+      <c r="Q89" s="25">
         <f t="shared" si="12"/>
         <v>18.399999999999999</v>
       </c>
-      <c r="R89" s="4">
+      <c r="R89" s="27">
         <f>15*Q89-P89-O89-F89</f>
         <v>86</v>
       </c>
-      <c r="S89" s="4">
-        <f t="shared" si="14"/>
-        <v>86</v>
-      </c>
-      <c r="T89" s="18"/>
-      <c r="U89" s="7">
+      <c r="S89" s="27">
+        <v>0</v>
+      </c>
+      <c r="T89" s="28"/>
+      <c r="U89" s="25">
         <f t="shared" si="15"/>
-        <v>15.000000000000002</v>
-      </c>
-      <c r="V89" s="7">
+        <v>10.32608695652174</v>
+      </c>
+      <c r="V89" s="25">
         <f t="shared" si="13"/>
         <v>10.32608695652174</v>
       </c>
-      <c r="W89" s="7">
+      <c r="W89" s="25">
         <v>18.2</v>
       </c>
-      <c r="X89" s="7">
+      <c r="X89" s="25">
         <v>9.6</v>
       </c>
-      <c r="Y89" s="7">
+      <c r="Y89" s="25">
         <v>16</v>
       </c>
-      <c r="Z89" s="7">
+      <c r="Z89" s="25">
         <v>7.2</v>
       </c>
-      <c r="AA89" s="7">
+      <c r="AA89" s="25">
         <v>9.4</v>
       </c>
-      <c r="AB89" s="7">
+      <c r="AB89" s="25">
         <v>15.6</v>
       </c>
-      <c r="AC89" s="7">
+      <c r="AC89" s="25">
         <v>7.8</v>
       </c>
-      <c r="AD89" s="7">
+      <c r="AD89" s="25">
         <v>14</v>
       </c>
-      <c r="AE89" s="7">
+      <c r="AE89" s="25">
         <v>16.600000000000001</v>
       </c>
-      <c r="AF89" s="7"/>
-      <c r="AG89" s="7">
+      <c r="AF89" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="AG89" s="25">
         <f t="shared" si="16"/>
-        <v>24.080000000000002</v>
+        <v>0</v>
       </c>
       <c r="AH89" s="7"/>
       <c r="AI89" s="7"/>
